--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484806_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484806_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.187</v>
+        <v>10.5138</v>
       </c>
       <c r="E2" t="n">
-        <v>8.5732</v>
+        <v>7.1117</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6138</v>
+        <v>3.4021</v>
       </c>
       <c r="G2" t="n">
         <v>7.7115</v>
@@ -610,13 +610,13 @@
         <v>2.8305</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9469</v>
+        <v>0.2738</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6576</v>
+        <v>0.1961</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2893</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>0.6415999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.8986</v>
+        <v>9.560499999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>8.0268</v>
+        <v>7.3448</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8718</v>
+        <v>2.2157</v>
       </c>
       <c r="G3" t="n">
         <v>4.1613</v>
@@ -688,13 +688,13 @@
         <v>1.887</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0581</v>
+        <v>0.72</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1968</v>
+        <v>0.5147</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1387</v>
+        <v>0.2052</v>
       </c>
       <c r="V3" t="n">
         <v>2.7922</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. BEDIA FERRER</t>
+          <t>P. LOPEZ DOMINGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.9619</v>
+        <v>7.3785</v>
       </c>
       <c r="E4" t="n">
-        <v>5.0728</v>
+        <v>4.2903</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8891</v>
+        <v>3.0882</v>
       </c>
       <c r="G4" t="n">
-        <v>3.294</v>
+        <v>4.8423</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8023</v>
+        <v>1.2991</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4917</v>
+        <v>3.5432</v>
       </c>
       <c r="J4" t="n">
-        <v>5.0496</v>
+        <v>5.9268</v>
       </c>
       <c r="K4" t="n">
-        <v>2.779</v>
+        <v>1.886</v>
       </c>
       <c r="L4" t="n">
-        <v>2.2707</v>
+        <v>4.0407</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7556</v>
+        <v>-1.0845</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9767</v>
+        <v>-0.5869</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7789</v>
+        <v>-0.4976</v>
       </c>
       <c r="P4" t="n">
-        <v>3.0192</v>
+        <v>2.4531</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R4" t="n">
-        <v>3.0192</v>
+        <v>3.3966</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3468</v>
+        <v>0.7247</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2787</v>
+        <v>-0.0514</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.776</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3018</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3018</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. LOPEZ DOMINGUEZ</t>
+          <t>J. BEDIA FERRER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>6.7397</v>
+        <v>7.1665</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4134</v>
+        <v>5.4625</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3262</v>
+        <v>1.704</v>
       </c>
       <c r="G5" t="n">
-        <v>4.8423</v>
+        <v>3.294</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2991</v>
+        <v>1.8023</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5432</v>
+        <v>1.4917</v>
       </c>
       <c r="J5" t="n">
-        <v>5.9268</v>
+        <v>5.0496</v>
       </c>
       <c r="K5" t="n">
-        <v>1.886</v>
+        <v>2.779</v>
       </c>
       <c r="L5" t="n">
-        <v>4.0407</v>
+        <v>2.2707</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0845</v>
+        <v>-1.7556</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5869</v>
+        <v>-0.9767</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4976</v>
+        <v>-0.7789</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4531</v>
+        <v>3.0192</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.3966</v>
+        <v>3.0192</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0859</v>
+        <v>0.5514</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9283</v>
+        <v>0.111</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0141</v>
+        <v>0.4404</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.3018</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.3018</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.9617</v>
+        <v>3.0592</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8025</v>
+        <v>0.8999</v>
       </c>
       <c r="F6" t="n">
         <v>2.1593</v>
@@ -922,10 +922,10 @@
         <v>2.4531</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0835</v>
+        <v>0.1809</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2787</v>
+        <v>-0.1813</v>
       </c>
       <c r="U6" t="n">
         <v>0.3622</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.6246</v>
+        <v>2.4311</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7629</v>
+        <v>0.8603</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8617</v>
+        <v>1.5707</v>
       </c>
       <c r="G7" t="n">
         <v>2.584</v>
@@ -1000,13 +1000,13 @@
         <v>2.2644</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2857</v>
+        <v>0.0922</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1735</v>
+        <v>-0.076</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4592</v>
+        <v>0.1682</v>
       </c>
       <c r="V7" t="n">
         <v>-1.566</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4391</v>
+        <v>2.3509</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2037</v>
+        <v>-0.4242</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6428</v>
+        <v>2.7751</v>
       </c>
       <c r="G8" t="n">
         <v>3.7394</v>
@@ -1078,13 +1078,13 @@
         <v>3.3966</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9606</v>
+        <v>-0.0488</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3398</v>
+        <v>-0.5603</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3792</v>
+        <v>0.5115</v>
       </c>
       <c r="V8" t="n">
         <v>-0.9624</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2453</v>
+        <v>1.6963</v>
       </c>
       <c r="E9" t="n">
-        <v>2.116</v>
+        <v>2.4083</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8707</v>
+        <v>-0.712</v>
       </c>
       <c r="G9" t="n">
         <v>0.4559</v>
@@ -1156,13 +1156,13 @@
         <v>0.3774</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5314</v>
+        <v>-0.0804</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2352</v>
+        <v>0.0572</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2963</v>
+        <v>-0.1375</v>
       </c>
       <c r="V9" t="n">
         <v>0.9434</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3476</v>
+        <v>0.2585</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7962</v>
+        <v>-0.991</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1438</v>
+        <v>1.2496</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6642</v>
@@ -1234,13 +1234,13 @@
         <v>1.3209</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3892</v>
+        <v>0.3001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3556</v>
+        <v>0.1608</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0335</v>
+        <v>0.1394</v>
       </c>
       <c r="V10" t="n">
         <v>1.2452</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.767</v>
+        <v>-1.7767</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9896</v>
+        <v>-3.1844</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2226</v>
+        <v>1.4078</v>
       </c>
       <c r="G11" t="n">
         <v>0.198</v>
@@ -1312,13 +1312,13 @@
         <v>1.6983</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2293</v>
+        <v>-0.239</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0559</v>
+        <v>-0.2508</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1734</v>
+        <v>0.0118</v>
       </c>
       <c r="V11" t="n">
         <v>-1.547</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>42.63849999999999</v>
+        <v>42.6386</v>
       </c>
       <c r="E12" t="n">
-        <v>23.7781</v>
+        <v>23.7782</v>
       </c>
       <c r="F12" t="n">
-        <v>18.8604</v>
+        <v>18.8605</v>
       </c>
       <c r="G12" t="n">
         <v>25.4457</v>
@@ -1390,13 +1390,13 @@
         <v>22.644</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4748</v>
+        <v>2.4749</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.08010000000000012</v>
+        <v>-0.0799999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>2.5546</v>
+        <v>2.5549</v>
       </c>
       <c r="V12" t="n">
         <v>2.4524</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LÓPEZ</t>
+          <t>V. BERENGUER DEL VALLE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,40 +1423,40 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2509</v>
+        <v>1.4587</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2509</v>
+        <v>1.9737</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-0.515</v>
       </c>
       <c r="G13" t="n">
-        <v>1.2509</v>
+        <v>1.217</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6339</v>
+        <v>-0.2833</v>
       </c>
       <c r="I13" t="n">
-        <v>0.617</v>
+        <v>1.5002</v>
       </c>
       <c r="J13" t="n">
-        <v>1.2509</v>
+        <v>1.9754</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6339</v>
+        <v>0.0423</v>
       </c>
       <c r="L13" t="n">
-        <v>0.617</v>
+        <v>1.9331</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-0.7584</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>-0.3256</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>-0.4329</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1468,28 +1468,28 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>0.1207</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>-0.0016</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>0.1223</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1211</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>0.1211</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V. BERENGUER DEL VALLE</t>
+          <t>J. GONZALEZ LÓPEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,40 +1501,40 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1135</v>
+        <v>1.2509</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6814</v>
+        <v>1.2509</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5679</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.217</v>
+        <v>1.2509</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2833</v>
+        <v>0.6339</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5002</v>
+        <v>0.617</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9754</v>
+        <v>1.2509</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0423</v>
+        <v>0.6339</v>
       </c>
       <c r="L14" t="n">
-        <v>1.9331</v>
+        <v>0.617</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7584</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3256</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4329</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1546,22 +1546,22 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2246</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2939</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0694</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1211</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1211</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4205</v>
+        <v>-1.0675</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2664</v>
+        <v>1.0716</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.687</v>
+        <v>-2.1391</v>
       </c>
       <c r="G15" t="n">
         <v>-2.4511</v>
@@ -1624,13 +1624,13 @@
         <v>1.5096</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4568</v>
+        <v>-0.1901</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6314</v>
+        <v>-0.8263</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0882</v>
+        <v>0.6361</v>
       </c>
       <c r="V15" t="n">
         <v>0.06419999999999999</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.6292</v>
+        <v>-3.3372</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3387</v>
+        <v>-0.0254</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.9679</v>
+        <v>-3.3118</v>
       </c>
       <c r="G16" t="n">
         <v>-1.3028</v>
@@ -1702,13 +1702,13 @@
         <v>1.1322</v>
       </c>
       <c r="S16" t="n">
-        <v>2.202</v>
+        <v>0.4941</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7752</v>
+        <v>0.4111</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4268</v>
+        <v>0.0829</v>
       </c>
       <c r="V16" t="n">
         <v>-1.585</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.9261</v>
+        <v>-3.5099</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7606</v>
+        <v>-1.3709</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.1655</v>
+        <v>-2.139</v>
       </c>
       <c r="G17" t="n">
         <v>-2.1448</v>
@@ -1780,13 +1780,13 @@
         <v>0.1887</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5361</v>
+        <v>-0.1199</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2939</v>
+        <v>0.0958</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2422</v>
+        <v>-0.2157</v>
       </c>
       <c r="V17" t="n">
         <v>-1.2452</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.2164</v>
+        <v>-3.8651</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.8893</v>
+        <v>-2.6944</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3271</v>
+        <v>-1.1707</v>
       </c>
       <c r="G18" t="n">
         <v>-3.0726</v>
@@ -1858,13 +1858,13 @@
         <v>1.5096</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0681</v>
+        <v>-0.7169</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9283</v>
+        <v>-0.7334000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1398</v>
+        <v>0.0165</v>
       </c>
       <c r="V18" t="n">
         <v>1.2452</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.1742</v>
+        <v>-5.3018</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.6091</v>
+        <v>-2.9989</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5651</v>
+        <v>-2.3029</v>
       </c>
       <c r="G19" t="n">
         <v>-3.3094</v>
@@ -1936,13 +1936,13 @@
         <v>0.7548</v>
       </c>
       <c r="S19" t="n">
-        <v>0.07870000000000001</v>
+        <v>-0.0488</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3121</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2333</v>
+        <v>0.0289</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6226</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.2717</v>
+        <v>-5.7521</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8492</v>
+        <v>-1.4594</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.4226</v>
+        <v>-4.2926</v>
       </c>
       <c r="G20" t="n">
         <v>-4.159</v>
@@ -2014,13 +2014,13 @@
         <v>1.1322</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1692</v>
+        <v>-0.6496</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0458</v>
+        <v>-0.6561</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1234</v>
+        <v>0.0065</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.0734</v>
+        <v>-6.324</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.064</v>
+        <v>-3.5769</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.0094</v>
+        <v>-2.7472</v>
       </c>
       <c r="G21" t="n">
         <v>-3.2799</v>
@@ -2092,13 +2092,13 @@
         <v>1.1322</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7254</v>
+        <v>0.0239</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6902</v>
+        <v>-0.203</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0352</v>
+        <v>0.227</v>
       </c>
       <c r="V21" t="n">
         <v>-1.181</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.093</v>
+        <v>-7.3149</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.8953</v>
+        <v>-5.4082</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1977</v>
+        <v>-1.9067</v>
       </c>
       <c r="G22" t="n">
         <v>-2.734</v>
@@ -2170,13 +2170,13 @@
         <v>1.5096</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2909</v>
+        <v>-0.5128</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9994</v>
+        <v>-0.5122</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2915</v>
+        <v>-0.0005</v>
       </c>
       <c r="V22" t="n">
         <v>-0.8603</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.198399999999999</v>
+        <v>-8.226100000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.3302</v>
+        <v>-5.6225</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8682</v>
+        <v>-2.6037</v>
       </c>
       <c r="G23" t="n">
         <v>-5.46</v>
@@ -2248,13 +2248,13 @@
         <v>1.5096</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1981</v>
+        <v>-0.2259</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2409</v>
+        <v>-0.0514</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4391</v>
+        <v>-0.1745</v>
       </c>
       <c r="V23" t="n">
         <v>1.6112</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-42.6385</v>
+        <v>-41.989</v>
       </c>
       <c r="E24" t="n">
-        <v>-18.8603</v>
+        <v>-18.8604</v>
       </c>
       <c r="F24" t="n">
-        <v>-23.7784</v>
+        <v>-23.1287</v>
       </c>
       <c r="G24" t="n">
         <v>-25.4457</v>
@@ -2326,13 +2326,13 @@
         <v>10.3785</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.474900000000001</v>
+        <v>-1.8253</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.5547</v>
+        <v>-2.5548</v>
       </c>
       <c r="U24" t="n">
-        <v>0.07990000000000003</v>
+        <v>0.7295</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4524</v>
